--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -67938,7 +67938,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6419675926</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>22601</v>
@@ -67959,6 +67959,32 @@
         <v>557</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493055556</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>33685</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.166999995708466</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -67964,7 +67964,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493055556</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>33685</v>
@@ -67985,6 +67985,32 @@
         <v>557</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6439351852</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>65562</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.166999995708466</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.165500000119209</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>983</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -67990,7 +67990,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6439351852</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>65562</v>
@@ -68011,6 +68011,32 @@
         <v>983</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6493518519</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>39164</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.161500006914139</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68016,7 +68016,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6493518519</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>39164</v>
@@ -68037,6 +68037,32 @@
         <v>557</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493171296</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>11963</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>0.166999995708466</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>0.166999995708466</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68042,7 +68042,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6493171296</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>11963</v>
@@ -68063,6 +68063,32 @@
         <v>557</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.5082638889</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>49125</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>526</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="985">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2964,6 +2964,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.165500000119209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162499994039536</t>
   </si>
 </sst>
 </file>
@@ -68068,7 +68071,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.5082638889</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>49125</v>
@@ -68089,6 +68092,32 @@
         <v>526</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493518519</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>1414</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>984</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="986">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2967,6 +2967,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.162499994039536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163499996066093</t>
   </si>
 </sst>
 </file>
@@ -68097,7 +68100,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493518519</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>1414</v>
@@ -68118,6 +68121,32 @@
         <v>984</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6269560185</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>3636</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.164499998092651</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.164499998092651</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>985</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68126,7 +68126,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6269560185</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>3636</v>
@@ -68147,6 +68147,32 @@
         <v>985</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495138889</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>87633</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.161500006914139</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.161500006914139</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68152,7 +68152,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495138889</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>87633</v>
@@ -68173,6 +68173,32 @@
         <v>557</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6493865741</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>88547</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68178,7 +68178,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493865741</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>88547</v>
@@ -68199,6 +68199,32 @@
         <v>527</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.630775463</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>17129</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>0.161500006914139</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>401</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68204,7 +68204,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.630775463</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>17129</v>
@@ -68225,6 +68225,32 @@
         <v>401</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6438078704</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>7001</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68230,7 +68230,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6438078704</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>7001</v>
@@ -68251,6 +68251,32 @@
         <v>557</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6910185185</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>51201</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>0.164499998092651</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>0.164499998092651</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="987">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2970,6 +2970,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.163499996066093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160500004887581</t>
   </si>
 </sst>
 </file>
@@ -68256,7 +68259,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6910185185</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>51201</v>
@@ -68277,6 +68280,32 @@
         <v>535</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6470138889</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>15235</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.160500004887581</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>986</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="988">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2973,6 +2973,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.160500004887581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159500002861023</t>
   </si>
 </sst>
 </file>
@@ -68285,7 +68288,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6470138889</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>15235</v>
@@ -68306,6 +68309,32 @@
         <v>986</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6846875</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>44420</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68314,7 +68314,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6846875</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>44420</v>
@@ -68335,6 +68335,32 @@
         <v>987</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911921296</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>25864</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68340,7 +68340,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911921296</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>25864</v>
@@ -68361,6 +68361,32 @@
         <v>535</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.642037037</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>26457</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.165000006556511</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>985</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68366,7 +68366,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.642037037</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>26457</v>
@@ -68387,6 +68387,32 @@
         <v>985</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910185185</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>6824</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.160500004887581</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="989">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2976,6 +2976,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.159500002861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157000005245209</t>
   </si>
 </sst>
 </file>
@@ -68392,7 +68395,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6910185185</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>6824</v>
@@ -68401,7 +68404,7 @@
         <v>0.163499996066093</v>
       </c>
       <c r="D2504" t="n">
-        <v>0.160500004887581</v>
+        <v>0.159500002861023</v>
       </c>
       <c r="E2504" t="n">
         <v>0.163499996066093</v>
@@ -68413,6 +68416,32 @@
         <v>987</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.691099537</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>56151</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>988</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="988">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2976,9 +2976,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.159500002861023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157000005245209</t>
   </si>
 </sst>
 </file>
@@ -68421,25 +68418,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.691099537</v>
+        <v>45967.6824652778</v>
       </c>
       <c r="B2505" t="n">
-        <v>56151</v>
+        <v>49477</v>
       </c>
       <c r="C2505" t="n">
         <v>0.159999996423721</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.155000001192093</v>
+        <v>0.153999999165535</v>
       </c>
       <c r="E2505" t="n">
+        <v>0.157499998807907</v>
+      </c>
+      <c r="F2505" t="n">
         <v>0.159500002861023</v>
       </c>
-      <c r="F2505" t="n">
-        <v>0.157000005245209</v>
-      </c>
       <c r="G2505" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68418,25 +68418,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6824652778</v>
+        <v>45968.6910532407</v>
       </c>
       <c r="B2505" t="n">
-        <v>49477</v>
+        <v>14710</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.159999996423721</v>
+        <v>0.158999994397163</v>
       </c>
       <c r="D2505" t="n">
         <v>0.153999999165535</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.157499998807907</v>
+        <v>0.153999999165535</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.159500002861023</v>
+        <v>0.155000001192093</v>
       </c>
       <c r="G2505" t="s">
-        <v>987</v>
+        <v>523</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="989">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2976,6 +2976,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.159500002861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157000005245209</t>
   </si>
 </sst>
 </file>
@@ -68418,27 +68421,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6910532407</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>56151</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>988</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>49477</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.157499998807907</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>14710</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>0.158999994397163</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>0.153999999165535</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>0.153999999165535</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>0.155000001192093</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>523</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6797800926</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>53255</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.156000003218651</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68499,7 +68499,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6797800926</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>53255</v>
@@ -68520,6 +68520,32 @@
         <v>987</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6330787037</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>23594</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>401</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68525,7 +68525,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6330787037</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>23594</v>
@@ -68546,6 +68546,32 @@
         <v>401</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6799421296</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>34041</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>947</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68551,7 +68551,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6799421296</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>34041</v>
@@ -68572,6 +68572,32 @@
         <v>947</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6212384259</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>26725</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.157499998807907</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>946</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68577,7 +68577,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6212384259</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>26725</v>
@@ -68598,6 +68598,32 @@
         <v>946</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6690856481</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68603,7 +68603,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6690856481</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>1900</v>
@@ -68624,6 +68624,32 @@
         <v>535</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6197685185</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>109679</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>0.165500000119209</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68629,7 +68629,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6197685185</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>109679</v>
@@ -68650,6 +68650,32 @@
         <v>527</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6605555556</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>112413</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>0.160500004887581</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>401</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68655,7 +68655,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6605555556</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>112413</v>
@@ -68676,6 +68676,32 @@
         <v>401</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6522916667</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>37300</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68681,7 +68681,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6522916667</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>37300</v>
@@ -68702,6 +68702,32 @@
         <v>987</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6639699074</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>34019</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>0.157000005245209</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>987</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68707,7 +68707,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6639699074</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>34019</v>
@@ -68728,6 +68728,32 @@
         <v>987</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6653587963</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>351121</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>0.157499998807907</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>985</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68733,7 +68733,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6653587963</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>351121</v>
@@ -68754,6 +68754,32 @@
         <v>985</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6286111111</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>0.163499996066093</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>985</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68759,7 +68759,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6286111111</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>5700</v>
@@ -68780,6 +68780,32 @@
         <v>985</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6869212963</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>20544</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>0.160500004887581</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>0.163000002503395</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68785,7 +68785,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6869212963</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>20544</v>
@@ -68806,6 +68806,32 @@
         <v>527</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6625462963</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>51540</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>0.168999999761581</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>0.167500004172325</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68811,7 +68811,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6625462963</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>51540</v>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68835,6 +68835,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.3333333333</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68861,6 +68861,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.3333333333</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68887,6 +68887,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.3333333333</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68913,6 +68913,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.3333333333</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68939,6 +68939,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.3333333333</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68965,6 +68965,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.3333333333</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -68991,6 +68991,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.3333333333</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69017,6 +69017,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69043,6 +69043,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.3333333333</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69069,6 +69069,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.3333333333</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69095,6 +69095,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.3333333333</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69121,6 +69121,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.3333333333</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69147,6 +69147,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.3333333333</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69173,6 +69173,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.3333333333</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69199,6 +69199,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69225,6 +69225,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.3333333333</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69251,6 +69251,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.3333333333</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69277,6 +69277,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.3333333333</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69303,6 +69303,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.3333333333</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69329,6 +69329,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.3333333333</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69355,6 +69355,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.3333333333</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2541" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69381,6 +69381,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.3333333333</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69407,6 +69407,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.3333333333</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69433,6 +69433,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.3333333333</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69459,6 +69459,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.3333333333</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69485,6 +69485,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.3333333333</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69511,6 +69511,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.3333333333</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69537,6 +69537,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46034.3333333333</v>
+      </c>
+      <c r="B2548" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2548" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69563,6 +69563,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2549">
+      <c r="A2549" s="1" t="n">
+        <v>46035.3333333333</v>
+      </c>
+      <c r="B2549" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2549" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="D2549" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E2549" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="F2549" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="G2549" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69568,24 +69568,50 @@
         <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
-        <v>0</v>
+        <v>64522</v>
       </c>
       <c r="C2549" t="n">
-        <v>0.166500002145767</v>
+        <v>0.156499996781349</v>
       </c>
       <c r="D2549" t="n">
-        <v>0.166500002145767</v>
+        <v>0.153999999165535</v>
       </c>
       <c r="E2549" t="n">
-        <v>0.166500002145767</v>
+        <v>0.156499996781349</v>
       </c>
       <c r="F2549" t="n">
-        <v>0.166500002145767</v>
+        <v>0.155000001192093</v>
       </c>
       <c r="G2549" t="s">
-        <v>982</v>
+        <v>523</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.3333333333</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>72017</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>0.151999995112419</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>0.151999995112419</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>551</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2979,6 +2979,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.157000005245209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152500003576279</t>
   </si>
 </sst>
 </file>
@@ -69615,6 +69618,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.3333333333</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>16613</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>0.152500003576279</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>0.152500003576279</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>0.152500003576279</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>989</v>
+      </c>
+      <c r="H2551" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69644,6 +69644,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2552">
+      <c r="A2552" s="1" t="n">
+        <v>46038.3333333333</v>
+      </c>
+      <c r="B2552" t="n">
+        <v>67586</v>
+      </c>
+      <c r="C2552" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="D2552" t="n">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="E2552" t="n">
+        <v>0.153500005602837</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>576</v>
+      </c>
+      <c r="H2552" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EEMS.MI.xlsx
+++ b/data/EEMS.MI.xlsx
@@ -69670,6 +69670,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46041.3333333333</v>
+      </c>
+      <c r="B2553" t="n">
+        <v>81100</v>
+      </c>
+      <c r="C2553" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>0.149000003933907</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>0.150999993085861</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>0.149000003933907</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>411</v>
+      </c>
+      <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
